--- a/outputs/analysis/emissoes_fidc_por_taxonomia.xlsx
+++ b/outputs/analysis/emissoes_fidc_por_taxonomia.xlsx
@@ -545,48 +545,48 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4.751893772390955</v>
+        <v>4.355347460331231</v>
       </c>
       <c r="C4" s="4">
         <f>B4/B$8</f>
-        <v>0.1162355734379187</v>
+        <v>0.10653569583443391</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>10.68514314594</v>
+        <v>9.715143145940001</v>
       </c>
       <c r="E4" s="4">
         <f>D4/D$8</f>
-        <v>0.12089098220744748</v>
+        <v>0.10991646823607587</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>5.933249373549046</v>
+        <v>5.35979568560877</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>10.93480114906</v>
+        <v>9.03480114906</v>
       </c>
       <c r="H4" s="4">
         <f>G4/G$8</f>
-        <v>0.1027095368376905</v>
+        <v>0.0848630193444677</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.2496580031199989</v>
+        <v>-0.6803419968800011</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.1399598732</v>
+        <v>4.0599598732</v>
       </c>
       <c r="K4" s="4">
         <f>J4/J$8</f>
-        <v>0.07893516038529944</v>
+        <v>0.07740982849218064</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>7.32031892482</v>
+        <v>5.705318924819999</v>
       </c>
       <c r="M4" s="4">
         <f>L4/L$8</f>
-        <v>0.11679855378529821</v>
+        <v>0.09103059663746195</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>3.18035905162</v>
+        <v>1.64535905162</v>
       </c>
     </row>
     <row r="5">
@@ -596,21 +596,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>10.43299846329051</v>
+        <v>8.725651793954372</v>
       </c>
       <c r="C5" s="4">
         <f>B5/B$8</f>
-        <v>0.2552004773556469</v>
+        <v>0.21343725017227638</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>21.4846035084</v>
+        <v>19.8036035084</v>
       </c>
       <c r="E5" s="4">
         <f>D5/D$8</f>
-        <v>0.24307534162094346</v>
+        <v>0.22405662204787577</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>11.05160504510949</v>
+        <v>11.07795171444563</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>28.71965699961</v>
@@ -620,7 +620,7 @@
         <v>0.2697609794962622</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>7.23505349121</v>
+        <v>8.916053491209999</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>19.39381267632</v>
@@ -630,14 +630,14 @@
         <v>0.3697750125545281</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>9.783637272329999</v>
+        <v>10.78363727233</v>
       </c>
       <c r="M5" s="4">
         <f>L5/L$8</f>
-        <v>0.15610176221880692</v>
+        <v>0.17205715364161575</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-9.61017540399</v>
+        <v>-8.61017540399</v>
       </c>
     </row>
     <row r="6">
@@ -647,48 +647,48 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>17.13055294499981</v>
+        <v>19.33358250441061</v>
       </c>
       <c r="C6" s="4">
         <f>B6/B$8</f>
-        <v>0.41902865262680344</v>
+        <v>0.47291672681452995</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>44.66609152533</v>
+        <v>46.91709152533</v>
       </c>
       <c r="E6" s="4">
         <f>D6/D$8</f>
-        <v>0.5053491190631926</v>
+        <v>0.5308167798359323</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>27.53553858033019</v>
+        <v>27.58350902091939</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>51.12676092368</v>
+        <v>52.42676092368</v>
       </c>
       <c r="H6" s="4">
         <f>G6/G$8</f>
-        <v>0.48022875431382867</v>
+        <v>0.4924395294407706</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>6.460669398349999</v>
+        <v>5.509669398349999</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>21.12168209032</v>
+        <v>21.60168209032</v>
       </c>
       <c r="K6" s="4">
         <f>J6/J$8</f>
-        <v>0.4027196916085114</v>
+        <v>0.4118716829672241</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>39.32799902597</v>
+        <v>40.39299902597</v>
       </c>
       <c r="M6" s="4">
         <f>L6/L$8</f>
-        <v>0.627493618335196</v>
+        <v>0.6444861102004874</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.20631693565</v>
+        <v>18.79131693565</v>
       </c>
     </row>
     <row r="7">
@@ -698,48 +698,48 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>8.566133770094378</v>
+        <v>8.466997192079447</v>
       </c>
       <c r="C7" s="4">
         <f>B7/B$8</f>
-        <v>0.209535296579631</v>
+        <v>0.20711032717875982</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>11.55076395418</v>
+        <v>11.95076395418</v>
       </c>
       <c r="E7" s="4">
         <f>D7/D$8</f>
-        <v>0.1306845571084164</v>
+        <v>0.13521012988011602</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>2.984630184085623</v>
+        <v>3.483766762100553</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15.6821287893</v>
+        <v>16.2821287893</v>
       </c>
       <c r="H7" s="4">
         <f>G7/G$8</f>
-        <v>0.14730072935221852</v>
+        <v>0.1529364717184994</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4.131364835119999</v>
+        <v>4.331364835119999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.79214732856</v>
+        <v>7.392147328559999</v>
       </c>
       <c r="K7" s="4">
         <f>J7/J$8</f>
-        <v>0.1485701354516612</v>
+        <v>0.14094347598606727</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>6.24278421138</v>
+        <v>5.79278421138</v>
       </c>
       <c r="M7" s="4">
         <f>L7/L$8</f>
-        <v>0.09960606566069888</v>
+        <v>0.0924261395204349</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-1.549363117179999</v>
+        <v>-1.599363117179999</v>
       </c>
     </row>
     <row r="8">
@@ -766,11 +766,11 @@
       </c>
       <c r="F8" s="5">
         <f>SUM(F4:F7)</f>
-        <v>47.50502318307435</v>
+        <v>47.505023183074336</v>
       </c>
       <c r="G8" s="5">
         <f>SUM(G4:G7)</f>
-        <v>106.46334786165</v>
+        <v>106.46334786164999</v>
       </c>
       <c r="H8" s="6">
         <f>G8/G$8</f>
@@ -790,7 +790,7 @@
       </c>
       <c r="L8" s="5">
         <f>SUM(L4:L7)</f>
-        <v>62.6747394345</v>
+        <v>62.674739434500005</v>
       </c>
       <c r="M8" s="6">
         <f>L8/L$8</f>
@@ -850,7 +850,7 @@
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5">
         <f>G8+G9</f>
-        <v>116.92131905477001</v>
+        <v>116.92131905477</v>
       </c>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
